--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXI/LTAIPT_A63F31B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXI/LTAIPT_A63F31B.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="57">
   <si>
     <t>48987</t>
   </si>
@@ -128,7 +128,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>Programático</t>
@@ -137,61 +137,58 @@
     <t>Cuenta pública</t>
   </si>
   <si>
-    <t>Dirección Académica, Subdirección de Planeación y Evaluación, Departamento de Programación y Presupuesto</t>
-  </si>
-  <si>
     <t>La Secretaría de Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente a lo programático, que forma parte de la cuenta pública.</t>
   </si>
   <si>
+    <t>Contable</t>
+  </si>
+  <si>
+    <t>Estados financieros</t>
+  </si>
+  <si>
+    <t>Departamento de Contabilidad</t>
+  </si>
+  <si>
+    <t>La Secretaría de Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente a la contabilidad, que forma parte de la cuenta pública.</t>
+  </si>
+  <si>
     <t>Presupuestal</t>
   </si>
   <si>
     <t>Departamento de Programación y Presupuesto</t>
   </si>
   <si>
-    <t>La Secretaría de Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su siti oficial la información referente al presupuesto, que forma parte de la cuenta pública.</t>
-  </si>
-  <si>
-    <t>Contable</t>
-  </si>
-  <si>
-    <t>Estados financieros</t>
-  </si>
-  <si>
-    <t>Departamento de Contabilidad</t>
-  </si>
-  <si>
-    <t>La Secretaría de Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente a la contabilidad, que forma parte de la cuenta pública.</t>
-  </si>
-  <si>
-    <t>3E04859A5CFB775F7BFA84F70FD78288</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Depto.%20de%20Programacion%20y%20Presupuesto/3er_Trimestre/Informacion%20Programatica/programatica_3er_trimestre.pdf</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>17/10/2022</t>
-  </si>
-  <si>
-    <t>DDC3FEC79D4CB8ECF4190FD60E875789</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Depto.%20de%20Programacion%20y%20Presupuesto/3er_Trimestre/Informacion%20Presupuestal/presupuestal_3er_trimestre.pdf</t>
-  </si>
-  <si>
-    <t>5BCCEF4250BF242A4DF60F534B85E1CC</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Depto.%20de%20Programacion%20y%20Presupuesto/3er_Trimestre/Informacion%20Contable/contabilidad_3er_trimestre.pdf</t>
+    <t>La Secretaría de Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente al presupuesto, que forma parte de la cuenta pública.</t>
+  </si>
+  <si>
+    <t>Subdirección de Planeación y Evaluación, Departamento de Programación y Presupuesto</t>
+  </si>
+  <si>
+    <t>18E90D692976504006137B73C6930E79</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/3er%20Trimestre/Informacion%20Contable.pdf</t>
+  </si>
+  <si>
+    <t>17/10/2023</t>
+  </si>
+  <si>
+    <t>B10E67E5D2C9A12F02A1FFFF0858FF91</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/3er%20Trimestre/Informacion%20Presupuestal.pdf</t>
+  </si>
+  <si>
+    <t>71CA63BA19F3C8BDC9D297818C2482B3</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/3er%20Trimestre/Informacion%20Programatica.pdf</t>
   </si>
 </sst>
 </file>
@@ -587,17 +584,17 @@
   <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="67.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="171.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="195" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="93.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="229" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="217.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
@@ -772,33 +769,33 @@
         <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>51</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="K8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>36</v>
@@ -810,33 +807,33 @@
         <v>50</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="K9" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>36</v>
@@ -848,28 +845,28 @@
         <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="K10" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -883,7 +880,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E191">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E195">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -898,12 +895,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
